--- a/artfynd/A 53440-2022 artfynd.xlsx
+++ b/artfynd/A 53440-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53440-2022 artfynd.xlsx
+++ b/artfynd/A 53440-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114687667</v>
+        <v>114687693</v>
       </c>
       <c r="B2" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862743</v>
+        <v>862706</v>
       </c>
       <c r="R2" t="n">
-        <v>7494874</v>
+        <v>7494979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,12 +776,7 @@
         <v>114687601</v>
       </c>
       <c r="B3" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114687675</v>
+        <v>114687609</v>
       </c>
       <c r="B4" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -921,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862530</v>
+        <v>863310</v>
       </c>
       <c r="R4" t="n">
-        <v>7495212</v>
+        <v>7495404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,17 +936,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Nära hotad (NT)</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114687689</v>
+        <v>114687673</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1004,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862551</v>
+        <v>862503</v>
       </c>
       <c r="R5" t="n">
-        <v>7495255</v>
+        <v>7495190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114687609</v>
+        <v>114687695</v>
       </c>
       <c r="B6" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863310</v>
+        <v>862740</v>
       </c>
       <c r="R6" t="n">
-        <v>7495404</v>
+        <v>7494941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,12 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,12 +1168,7 @@
         <v>114687688</v>
       </c>
       <c r="B7" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,37 +1263,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114687673</v>
+        <v>114687692</v>
       </c>
       <c r="B8" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>2166</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862503</v>
+        <v>862698</v>
       </c>
       <c r="R8" t="n">
-        <v>7495190</v>
+        <v>7494974</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,12 +1328,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,37 +1361,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114687695</v>
+        <v>114687696</v>
       </c>
       <c r="B9" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>2166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1396,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862740</v>
+        <v>862760</v>
       </c>
       <c r="R9" t="n">
-        <v>7494941</v>
+        <v>7494924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,15 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114687687</v>
+        <v>114687667</v>
       </c>
       <c r="B10" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>862545</v>
+        <v>862743</v>
       </c>
       <c r="R10" t="n">
-        <v>7495228</v>
+        <v>7494874</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114687693</v>
+        <v>114687675</v>
       </c>
       <c r="B11" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862706</v>
+        <v>862530</v>
       </c>
       <c r="R11" t="n">
-        <v>7494979</v>
+        <v>7495212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,12 +1622,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nära hotad (NT)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,15 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114687696</v>
+        <v>114687668</v>
       </c>
       <c r="B12" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,34 +1671,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2166</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Riukanjärvi, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862760</v>
+        <v>862727</v>
       </c>
       <c r="R12" t="n">
-        <v>7494924</v>
+        <v>7494934</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,12 +1730,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1813,15 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114687668</v>
+        <v>114687657</v>
       </c>
       <c r="B13" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,39 +1774,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riukanjärvi, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862727</v>
+        <v>862764</v>
       </c>
       <c r="R13" t="n">
-        <v>7494934</v>
+        <v>7494870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,15 +1861,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114687692</v>
+        <v>114687687</v>
       </c>
       <c r="B14" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,21 +1872,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2166</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1961,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862698</v>
+        <v>862545</v>
       </c>
       <c r="R14" t="n">
-        <v>7494974</v>
+        <v>7495228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,12 +1926,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,15 +1959,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114687657</v>
+        <v>114687689</v>
       </c>
       <c r="B15" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,10 +1994,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862764</v>
+        <v>862551</v>
       </c>
       <c r="R15" t="n">
-        <v>7494870</v>
+        <v>7495255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 53440-2022 artfynd.xlsx
+++ b/artfynd/A 53440-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,45 +1763,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114687657</v>
+        <v>134752672</v>
       </c>
       <c r="B13" t="n">
-        <v>97983</v>
+        <v>58410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Riukanjärvi, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862764</v>
+        <v>862641</v>
       </c>
       <c r="R13" t="n">
-        <v>7494870</v>
+        <v>7494947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,12 +1837,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1845,7 +1864,6 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -1861,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114687687</v>
+        <v>134752673</v>
       </c>
       <c r="B14" t="n">
-        <v>97983</v>
+        <v>58596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,34 +1890,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>103041</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Riukanjärvi, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862545</v>
+        <v>862753</v>
       </c>
       <c r="R14" t="n">
-        <v>7495228</v>
+        <v>7494904</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1926,12 +1953,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1943,7 +1980,6 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
@@ -1959,7 +1995,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114687689</v>
+        <v>114687657</v>
       </c>
       <c r="B15" t="n">
         <v>97983</v>
@@ -1994,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862551</v>
+        <v>862764</v>
       </c>
       <c r="R15" t="n">
-        <v>7495255</v>
+        <v>7494870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,6 +2090,202 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114687687</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Riukanjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>862545</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7495228</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114687689</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Riukanjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>862551</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7495255</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53440-2022 artfynd.xlsx
+++ b/artfynd/A 53440-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687695</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687696</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687667</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687668</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752672</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752673</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687657</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687693</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687601</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687609</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687673</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687688</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687692</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687675</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2188,6 +2263,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687687</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2286,8 +2366,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687689</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>